--- a/171/food/2026-01-14-sm.xlsx
+++ b/171/food/2026-01-14-sm.xlsx
@@ -320,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -419,12 +419,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -844,8 +838,8 @@
           <t>МБОУ "СОШ им.Б.Н.Жабраилова с. Шовхал-Берды"</t>
         </is>
       </c>
-      <c r="C1" s="40" t="n"/>
-      <c r="D1" s="41" t="n"/>
+      <c r="C1" s="38" t="n"/>
+      <c r="D1" s="39" t="n"/>
       <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Отд./корп</t>
@@ -860,7 +854,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>14.01.2026</t>
         </is>
       </c>
     </row>
@@ -939,7 +933,7 @@
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>Омлет с сыром</t>
+          <t>Омлет с сыром №275</t>
         </is>
       </c>
       <c r="E4" s="21" t="n">
@@ -948,16 +942,16 @@
       <c r="F4" s="22" t="n">
         <v>26.55</v>
       </c>
-      <c r="G4" s="42" t="n">
-        <v>287.5</v>
-      </c>
-      <c r="H4" s="42" t="n">
+      <c r="G4" s="21" t="n">
+        <v>276</v>
+      </c>
+      <c r="H4" s="40" t="n">
         <v>16.9</v>
       </c>
-      <c r="I4" s="42" t="n">
+      <c r="I4" s="40" t="n">
         <v>23.3</v>
       </c>
-      <c r="J4" s="43" t="n">
+      <c r="J4" s="41" t="n">
         <v>2.8</v>
       </c>
     </row>
@@ -987,23 +981,23 @@
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
-          <t>Чай с лимоном</t>
+          <t>Чай с лимоном №459</t>
         </is>
       </c>
       <c r="E6" s="30" t="n">
         <v>180</v>
       </c>
-      <c r="F6" s="44" t="n">
+      <c r="F6" s="42" t="n">
         <v>35.3</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H6" s="28" t="e"/>
-      <c r="I6" s="44" t="n">
+      <c r="I6" s="42" t="n">
         <v>0.1</v>
       </c>
-      <c r="J6" s="45" t="n">
+      <c r="J6" s="43" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -1014,11 +1008,7 @@
           <t>хлеб</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
+      <c r="C7" s="27" t="e"/>
       <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Хлеб пшеничный</t>
@@ -1030,16 +1020,16 @@
       <c r="F7" s="33" t="n">
         <v>10.58</v>
       </c>
-      <c r="G7" s="44" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="H7" s="44" t="n">
+      <c r="G7" s="42" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="H7" s="42" t="n">
         <v>4.7</v>
       </c>
-      <c r="I7" s="44" t="n">
+      <c r="I7" s="42" t="n">
         <v>0.6</v>
       </c>
-      <c r="J7" s="45" t="n">
+      <c r="J7" s="43" t="n">
         <v>24.1</v>
       </c>
     </row>
@@ -1057,7 +1047,7 @@
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>Яблоко</t>
+          <t>Яблоко №338</t>
         </is>
       </c>
       <c r="E8" s="30" t="n">
@@ -1066,16 +1056,16 @@
       <c r="F8" s="33" t="n">
         <v>17.64</v>
       </c>
-      <c r="G8" s="44" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="H8" s="44" t="n">
+      <c r="G8" s="42" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="H8" s="42" t="n">
         <v>1.2</v>
       </c>
-      <c r="I8" s="44" t="n">
+      <c r="I8" s="42" t="n">
         <v>0.4</v>
       </c>
-      <c r="J8" s="45" t="n">
+      <c r="J8" s="43" t="n">
         <v>16.8</v>
       </c>
     </row>
@@ -1093,25 +1083,25 @@
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
-          <t>Масло сливочное (порциями)</t>
+          <t>Масло сливочное (порциями) №14</t>
         </is>
       </c>
       <c r="E9" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="42" t="n">
         <v>1.7</v>
       </c>
-      <c r="G9" s="44" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="H9" s="44" t="n">
+      <c r="G9" s="42" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H9" s="42" t="n">
         <v>0.1</v>
       </c>
-      <c r="I9" s="44" t="n">
+      <c r="I9" s="42" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J9" s="45" t="n">
+      <c r="J9" s="43" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1138,14 +1128,34 @@
           <t>закуска</t>
         </is>
       </c>
-      <c r="C11" s="19" t="e"/>
-      <c r="D11" s="20" t="e"/>
-      <c r="E11" s="34" t="e"/>
-      <c r="F11" s="34" t="e"/>
-      <c r="G11" s="34" t="e"/>
-      <c r="H11" s="34" t="e"/>
-      <c r="I11" s="34" t="e"/>
-      <c r="J11" s="35" t="e"/>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Салат из моркови с сухофруктами №24</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>86</v>
+      </c>
+      <c r="H11" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I11" s="40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J11" s="41" t="n">
+        <v>9.699999999999999</v>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="25" t="e"/>
@@ -1154,14 +1164,34 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="C12" s="27" t="e"/>
-      <c r="D12" s="26" t="e"/>
-      <c r="E12" s="28" t="e"/>
-      <c r="F12" s="28" t="e"/>
-      <c r="G12" s="28" t="e"/>
-      <c r="H12" s="28" t="e"/>
-      <c r="I12" s="28" t="e"/>
-      <c r="J12" s="29" t="e"/>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Борщ №81</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>250</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="G12" s="30" t="n">
+        <v>171</v>
+      </c>
+      <c r="H12" s="42" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I12" s="42" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J12" s="43" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="25" t="e"/>
@@ -1170,14 +1200,34 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="C13" s="27" t="e"/>
-      <c r="D13" s="26" t="e"/>
-      <c r="E13" s="28" t="e"/>
-      <c r="F13" s="28" t="e"/>
-      <c r="G13" s="28" t="e"/>
-      <c r="H13" s="28" t="e"/>
-      <c r="I13" s="28" t="e"/>
-      <c r="J13" s="29" t="e"/>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Макаронные изделия отварные с маслом №203</t>
+        </is>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>120</v>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>182</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J13" s="43" t="n">
+        <v>30.5</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="25" t="e"/>
@@ -1202,14 +1252,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="C15" s="27" t="e"/>
-      <c r="D15" s="26" t="e"/>
-      <c r="E15" s="28" t="e"/>
-      <c r="F15" s="28" t="e"/>
-      <c r="G15" s="28" t="e"/>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>200</v>
+      </c>
+      <c r="F15" s="33" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>39</v>
+      </c>
       <c r="H15" s="28" t="e"/>
-      <c r="I15" s="28" t="e"/>
-      <c r="J15" s="29" t="e"/>
+      <c r="I15" s="42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J15" s="43" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="25" t="e"/>
@@ -1219,53 +1287,105 @@
         </is>
       </c>
       <c r="C16" s="27" t="e"/>
-      <c r="D16" s="26" t="e"/>
-      <c r="E16" s="28" t="e"/>
-      <c r="F16" s="28" t="e"/>
-      <c r="G16" s="28" t="e"/>
-      <c r="H16" s="28" t="e"/>
-      <c r="I16" s="28" t="e"/>
-      <c r="J16" s="29" t="e"/>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" s="33" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="G16" s="30" t="n">
+        <v>133</v>
+      </c>
+      <c r="H16" s="42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I16" s="42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="43" t="n">
+        <v>24.1</v>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="25" t="e"/>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>хлеб черн.</t>
+          <t>кисломол.</t>
         </is>
       </c>
       <c r="C17" s="27" t="e"/>
-      <c r="D17" s="26" t="e"/>
-      <c r="E17" s="28" t="e"/>
-      <c r="F17" s="28" t="e"/>
-      <c r="G17" s="28" t="e"/>
-      <c r="H17" s="28" t="e"/>
-      <c r="I17" s="28" t="e"/>
-      <c r="J17" s="29" t="e"/>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Масло сливочное (порциями) №14</t>
+        </is>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>75</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I17" s="42" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J17" s="43" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="25" t="e"/>
-      <c r="B18" s="26" t="e"/>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>кисломол.</t>
+        </is>
+      </c>
       <c r="C18" s="27" t="e"/>
-      <c r="D18" s="26" t="e"/>
-      <c r="E18" s="28" t="e"/>
-      <c r="F18" s="28" t="e"/>
-      <c r="G18" s="28" t="e"/>
-      <c r="H18" s="28" t="e"/>
-      <c r="I18" s="28" t="e"/>
-      <c r="J18" s="29" t="e"/>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>Сметана</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="33" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>19</v>
+      </c>
+      <c r="H18" s="42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="43" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="36" t="e"/>
-      <c r="B19" s="37" t="e"/>
-      <c r="C19" s="38" t="e"/>
-      <c r="D19" s="37" t="e"/>
-      <c r="E19" s="38" t="e"/>
-      <c r="F19" s="38" t="e"/>
-      <c r="G19" s="38" t="e"/>
-      <c r="H19" s="38" t="e"/>
-      <c r="I19" s="38" t="e"/>
-      <c r="J19" s="39" t="e"/>
+      <c r="A19" s="34" t="e"/>
+      <c r="B19" s="35" t="e"/>
+      <c r="C19" s="36" t="e"/>
+      <c r="D19" s="35" t="e"/>
+      <c r="E19" s="36" t="e"/>
+      <c r="F19" s="36" t="e"/>
+      <c r="G19" s="36" t="e"/>
+      <c r="H19" s="36" t="e"/>
+      <c r="I19" s="36" t="e"/>
+      <c r="J19" s="37" t="e"/>
     </row>
   </sheetData>
   <mergeCells count="1">
